--- a/InputData/indst/IFStE/Indst Fuels Subject to Electrification.xlsx
+++ b/InputData/indst/IFStE/Indst Fuels Subject to Electrification.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\IFStE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\IFStE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8F182F-B3F9-4C66-BA27-F718955C1631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817E8475-C6F2-4026-B6A5-72631990459F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4275" yWindow="-13455" windowWidth="17325" windowHeight="11040" xr2:uid="{CEBBDD15-8244-44C2-A2EB-EB506D69E415}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" xr2:uid="{CEBBDD15-8244-44C2-A2EB-EB506D69E415}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Source:</t>
   </si>
@@ -211,12 +211,6 @@
   </si>
   <si>
     <t>shifting levers will not work correctly in the model.  Leave electricity and hydrogen set to zero for all industries.</t>
-  </si>
-  <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
   </si>
   <si>
     <t>IFStFS Industrial Fuels Subject to Electrification</t>
@@ -614,14 +608,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D74327C6-C2CB-4CD6-A944-44D7EC17E747}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,69 +623,69 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -707,14 +701,14 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.26953125" customWidth="1"/>
-    <col min="2" max="13" width="13.1796875" customWidth="1"/>
+    <col min="1" max="1" width="46.28515625" customWidth="1"/>
+    <col min="2" max="11" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -748,14 +742,8 @@
       <c r="K1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -789,14 +777,8 @@
       <c r="K2" s="8">
         <v>0</v>
       </c>
-      <c r="L2" s="8">
-        <v>0</v>
-      </c>
-      <c r="M2" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -830,14 +812,8 @@
       <c r="K3" s="8">
         <v>0</v>
       </c>
-      <c r="L3" s="8">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -871,14 +847,8 @@
       <c r="K4" s="8">
         <v>0</v>
       </c>
-      <c r="L4" s="8">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -912,14 +882,8 @@
       <c r="K5" s="8">
         <v>0</v>
       </c>
-      <c r="L5" s="8">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -953,14 +917,8 @@
       <c r="K6" s="8">
         <v>0</v>
       </c>
-      <c r="L6" s="8">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -994,14 +952,8 @@
       <c r="K7" s="8">
         <v>0</v>
       </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1035,14 +987,8 @@
       <c r="K8" s="8">
         <v>0</v>
       </c>
-      <c r="L8" s="8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1076,14 +1022,8 @@
       <c r="K9" s="8">
         <v>0</v>
       </c>
-      <c r="L9" s="8">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1117,14 +1057,8 @@
       <c r="K10" s="8">
         <v>0</v>
       </c>
-      <c r="L10" s="8">
-        <v>0</v>
-      </c>
-      <c r="M10" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1158,14 +1092,8 @@
       <c r="K11" s="8">
         <v>0</v>
       </c>
-      <c r="L11" s="8">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1199,14 +1127,8 @@
       <c r="K12" s="8">
         <v>0</v>
       </c>
-      <c r="L12" s="8">
-        <v>0</v>
-      </c>
-      <c r="M12" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1240,14 +1162,8 @@
       <c r="K13" s="8">
         <v>0</v>
       </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1281,14 +1197,8 @@
       <c r="K14" s="8">
         <v>0</v>
       </c>
-      <c r="L14" s="8">
-        <v>0</v>
-      </c>
-      <c r="M14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1322,14 +1232,8 @@
       <c r="K15" s="8">
         <v>0</v>
       </c>
-      <c r="L15" s="8">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1363,14 +1267,8 @@
       <c r="K16" s="8">
         <v>0</v>
       </c>
-      <c r="L16" s="8">
-        <v>0</v>
-      </c>
-      <c r="M16" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1404,14 +1302,8 @@
       <c r="K17" s="8">
         <v>0</v>
       </c>
-      <c r="L17" s="8">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1445,14 +1337,8 @@
       <c r="K18" s="8">
         <v>0</v>
       </c>
-      <c r="L18" s="8">
-        <v>0</v>
-      </c>
-      <c r="M18" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1486,14 +1372,8 @@
       <c r="K19" s="8">
         <v>0</v>
       </c>
-      <c r="L19" s="8">
-        <v>0</v>
-      </c>
-      <c r="M19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -1527,14 +1407,8 @@
       <c r="K20" s="8">
         <v>0</v>
       </c>
-      <c r="L20" s="8">
-        <v>0</v>
-      </c>
-      <c r="M20" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1568,14 +1442,8 @@
       <c r="K21" s="8">
         <v>0</v>
       </c>
-      <c r="L21" s="8">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1609,14 +1477,8 @@
       <c r="K22" s="8">
         <v>0</v>
       </c>
-      <c r="L22" s="8">
-        <v>0</v>
-      </c>
-      <c r="M22" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1650,14 +1512,8 @@
       <c r="K23" s="8">
         <v>0</v>
       </c>
-      <c r="L23" s="8">
-        <v>0</v>
-      </c>
-      <c r="M23" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -1691,14 +1547,8 @@
       <c r="K24" s="8">
         <v>0</v>
       </c>
-      <c r="L24" s="8">
-        <v>0</v>
-      </c>
-      <c r="M24" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -1732,14 +1582,8 @@
       <c r="K25" s="8">
         <v>0</v>
       </c>
-      <c r="L25" s="8">
-        <v>0</v>
-      </c>
-      <c r="M25" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -1771,12 +1615,6 @@
         <v>1</v>
       </c>
       <c r="K26" s="8">
-        <v>0</v>
-      </c>
-      <c r="L26" s="8">
-        <v>0</v>
-      </c>
-      <c r="M26" s="8">
         <v>0</v>
       </c>
     </row>
